--- a/3_output/2026/w29/y2026_w29_weekly_report_output.xlsx
+++ b/3_output/2026/w29/y2026_w29_weekly_report_output.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="408">
   <si>
     <t>GRAPH 1A: Vector index for the current week</t>
   </si>
@@ -761,6 +761,18 @@
   </si>
   <si>
     <t xml:space="preserve">23.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.67</t>
   </si>
   <si>
     <t xml:space="preserve">23.56</t>
@@ -2316,7 +2328,7 @@
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -2410,17 +2422,27 @@
       <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
+      <c r="C7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>15.6667</v>
+      </c>
       <c r="E7" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -2451,17 +2473,27 @@
       <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>28.7</v>
+      </c>
       <c r="E8" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
+      <c r="G8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -2492,17 +2524,27 @@
       <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
+      <c r="C9" s="14" t="n">
+        <v>2.7333</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>15.4</v>
+      </c>
       <c r="E9" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
+      <c r="G9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -2533,17 +2575,27 @@
       <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
+      <c r="C10" s="14" t="n">
+        <v>2.1111</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>22.5556</v>
+      </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
+      <c r="G10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -3372,25 +3424,25 @@
         <v>29.0</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D26" s="26" t="n">
         <v>0.24</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F26" s="26" t="n">
         <v>0.44</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H26" s="26" t="n">
         <v>0.46</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J26" s="26" t="n">
         <v>0.26</v>
@@ -4082,7 +4134,7 @@
     <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -4170,13 +4222,27 @@
       <c r="B41" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
+      <c r="C41" s="31" t="n">
+        <v>27</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>141</v>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>168</v>
+      </c>
+      <c r="F41" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>18.67</v>
+      </c>
       <c r="J41" s="12"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -4207,13 +4273,27 @@
       <c r="B42" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
+      <c r="C42" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>287</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>351</v>
+      </c>
+      <c r="F42" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="I42" s="14" t="n">
+        <v>35.1</v>
+      </c>
       <c r="J42" s="12"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -4244,13 +4324,27 @@
       <c r="B43" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
+      <c r="C43" s="31" t="n">
+        <v>41</v>
+      </c>
+      <c r="D43" s="31" t="n">
+        <v>231</v>
+      </c>
+      <c r="E43" s="31" t="n">
+        <v>272</v>
+      </c>
+      <c r="F43" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>18.13</v>
+      </c>
       <c r="J43" s="12"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -4281,13 +4375,27 @@
       <c r="B44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
+      <c r="C44" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>203</v>
+      </c>
+      <c r="E44" s="31" t="n">
+        <v>222</v>
+      </c>
+      <c r="F44" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>24.67</v>
+      </c>
       <c r="J44" s="12"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -5120,43 +5228,43 @@
         <v>29.0</v>
       </c>
       <c r="C60" s="33" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="D60" s="31" t="n">
         <v>92.44</v>
       </c>
       <c r="E60" s="33" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="F60" s="31" t="n">
         <v>182.39</v>
       </c>
       <c r="G60" s="33" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="H60" s="31" t="n">
         <v>160.99</v>
       </c>
       <c r="I60" s="33" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="J60" s="31" t="n">
         <v>79.76</v>
       </c>
       <c r="K60" s="33" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L60" s="31" t="n">
         <v>135.15</v>
       </c>
       <c r="M60" s="33" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="N60" s="33" t="s">
         <v>105</v>
       </c>
       <c r="O60" s="33" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P60" s="1"/>
       <c r="Q60" s="12"/>
@@ -5828,7 +5936,7 @@
     <row r="73">
       <c r="A73" s="1"/>
       <c r="B73" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C73" s="36" t="s">
         <v>4</v>
@@ -5891,9 +5999,15 @@
       <c r="B74" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C74" s="31"/>
-      <c r="D74" s="31"/>
-      <c r="E74" s="31"/>
+      <c r="C74" s="31" t="n">
+        <v>27</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>141</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>168</v>
+      </c>
       <c r="F74" s="31" t="n">
         <v>9</v>
       </c>
@@ -5946,9 +6060,15 @@
       <c r="B75" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
+      <c r="C75" s="31" t="n">
+        <v>64</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>287</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>351</v>
+      </c>
       <c r="F75" s="31" t="n">
         <v>13</v>
       </c>
@@ -6001,9 +6121,15 @@
       <c r="B76" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="31"/>
-      <c r="D76" s="31"/>
-      <c r="E76" s="31"/>
+      <c r="C76" s="31" t="n">
+        <v>41</v>
+      </c>
+      <c r="D76" s="31" t="n">
+        <v>231</v>
+      </c>
+      <c r="E76" s="31" t="n">
+        <v>272</v>
+      </c>
       <c r="F76" s="31" t="n">
         <v>16</v>
       </c>
@@ -6056,9 +6182,15 @@
       <c r="B77" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C77" s="31"/>
-      <c r="D77" s="31"/>
-      <c r="E77" s="31"/>
+      <c r="C77" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>203</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>222</v>
+      </c>
       <c r="F77" s="31" t="n">
         <v>6</v>
       </c>
@@ -6120,24 +6252,12 @@
       <c r="E78" s="32" t="n">
         <v>1013</v>
       </c>
-      <c r="F78" s="32" t="n">
-        <v>44</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>48</v>
-      </c>
-      <c r="H78" s="32" t="n">
-        <v>92</v>
-      </c>
-      <c r="I78" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="F78" s="32"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="32"/>
+      <c r="I78" s="32"/>
+      <c r="J78" s="32"/>
+      <c r="K78" s="32"/>
       <c r="L78" s="32" t="n">
         <v>0</v>
       </c>
@@ -6926,7 +7046,7 @@
         <v>56</v>
       </c>
       <c r="O92" s="16" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
@@ -39041,58 +39161,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="L1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="M1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="P1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Q1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="R1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2">
@@ -39100,7 +39220,7 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="n">
@@ -39110,25 +39230,25 @@
         <v>46216</v>
       </c>
       <c r="F2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M2" t="b">
         <v>0</v>
@@ -39143,7 +39263,7 @@
         <v>50</v>
       </c>
       <c r="Q2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -39154,7 +39274,7 @@
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="n">
@@ -39164,25 +39284,25 @@
         <v>46216</v>
       </c>
       <c r="F3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
@@ -39197,7 +39317,7 @@
         <v>24</v>
       </c>
       <c r="Q3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -39208,7 +39328,7 @@
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="n">
@@ -39218,25 +39338,25 @@
         <v>46216</v>
       </c>
       <c r="F4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I4" t="s">
+        <v>135</v>
+      </c>
+      <c r="J4" t="s">
+        <v>137</v>
+      </c>
+      <c r="K4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L4" t="s">
         <v>139</v>
-      </c>
-      <c r="I4" t="s">
-        <v>131</v>
-      </c>
-      <c r="J4" t="s">
-        <v>133</v>
-      </c>
-      <c r="K4" t="s">
-        <v>134</v>
-      </c>
-      <c r="L4" t="s">
-        <v>135</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -39251,7 +39371,7 @@
         <v>50</v>
       </c>
       <c r="Q4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -39262,7 +39382,7 @@
         <v>2026</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="n">
@@ -39272,25 +39392,25 @@
         <v>46216</v>
       </c>
       <c r="F5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -39305,7 +39425,7 @@
         <v>50</v>
       </c>
       <c r="Q5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -39316,7 +39436,7 @@
         <v>2026</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="n">
@@ -39326,25 +39446,25 @@
         <v>46216</v>
       </c>
       <c r="F6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
@@ -39359,7 +39479,7 @@
         <v>50</v>
       </c>
       <c r="Q6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -39370,7 +39490,7 @@
         <v>2026</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="n">
@@ -39380,25 +39500,25 @@
         <v>46216</v>
       </c>
       <c r="F7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
@@ -39413,7 +39533,7 @@
         <v>50</v>
       </c>
       <c r="Q7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -39424,7 +39544,7 @@
         <v>2026</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="n">
@@ -39434,25 +39554,25 @@
         <v>46216</v>
       </c>
       <c r="F8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K8" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -39467,7 +39587,7 @@
         <v>50</v>
       </c>
       <c r="Q8" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -39478,7 +39598,7 @@
         <v>2026</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="n">
@@ -39488,25 +39608,25 @@
         <v>46216</v>
       </c>
       <c r="F9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G9" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H9" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I9" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M9" t="b">
         <v>0</v>
@@ -39519,7 +39639,7 @@
         <v>28</v>
       </c>
       <c r="Q9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -39530,7 +39650,7 @@
         <v>2026</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="n">
@@ -39540,25 +39660,25 @@
         <v>46216</v>
       </c>
       <c r="F10" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H10" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K10" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M10" t="b">
         <v>0</v>
@@ -39571,7 +39691,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -39582,7 +39702,7 @@
         <v>2026</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="n">
@@ -39592,25 +39712,25 @@
         <v>46216</v>
       </c>
       <c r="F11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G11" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I11" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M11" t="b">
         <v>0</v>
@@ -39623,7 +39743,7 @@
         <v>6</v>
       </c>
       <c r="Q11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -39634,7 +39754,7 @@
         <v>2026</v>
       </c>
       <c r="B12" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="n">
@@ -39644,25 +39764,25 @@
         <v>46216</v>
       </c>
       <c r="F12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H12" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I12" t="s">
+        <v>160</v>
+      </c>
+      <c r="J12" t="s">
+        <v>163</v>
+      </c>
+      <c r="K12" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12" t="s">
         <v>156</v>
-      </c>
-      <c r="J12" t="s">
-        <v>159</v>
-      </c>
-      <c r="K12" t="s">
-        <v>134</v>
-      </c>
-      <c r="L12" t="s">
-        <v>152</v>
       </c>
       <c r="M12" t="b">
         <v>0</v>
@@ -39675,7 +39795,7 @@
         <v>4</v>
       </c>
       <c r="Q12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -39686,7 +39806,7 @@
         <v>2026</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="n">
@@ -39696,25 +39816,25 @@
         <v>46216</v>
       </c>
       <c r="F13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G13" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I13" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K13" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L13" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M13" t="b">
         <v>0</v>
@@ -39727,7 +39847,7 @@
         <v>21</v>
       </c>
       <c r="Q13" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -39738,7 +39858,7 @@
         <v>2026</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="n">
@@ -39748,25 +39868,25 @@
         <v>46216</v>
       </c>
       <c r="F14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H14" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I14" t="s">
+        <v>160</v>
+      </c>
+      <c r="J14" t="s">
+        <v>137</v>
+      </c>
+      <c r="K14" t="s">
+        <v>138</v>
+      </c>
+      <c r="L14" t="s">
         <v>156</v>
-      </c>
-      <c r="J14" t="s">
-        <v>133</v>
-      </c>
-      <c r="K14" t="s">
-        <v>134</v>
-      </c>
-      <c r="L14" t="s">
-        <v>152</v>
       </c>
       <c r="M14" t="b">
         <v>0</v>
@@ -39779,7 +39899,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -39790,7 +39910,7 @@
         <v>2026</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="n">
@@ -39800,25 +39920,25 @@
         <v>46216</v>
       </c>
       <c r="F15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G15" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H15" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I15" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J15" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K15" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M15" t="b">
         <v>0</v>
@@ -39831,7 +39951,7 @@
         <v>15</v>
       </c>
       <c r="Q15" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -39842,7 +39962,7 @@
         <v>2026</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="n">
@@ -39852,25 +39972,25 @@
         <v>46216</v>
       </c>
       <c r="F16" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H16" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I16" t="s">
+        <v>160</v>
+      </c>
+      <c r="J16" t="s">
+        <v>137</v>
+      </c>
+      <c r="K16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L16" t="s">
         <v>156</v>
-      </c>
-      <c r="J16" t="s">
-        <v>133</v>
-      </c>
-      <c r="K16" t="s">
-        <v>134</v>
-      </c>
-      <c r="L16" t="s">
-        <v>152</v>
       </c>
       <c r="M16" t="b">
         <v>0</v>
@@ -39883,7 +40003,7 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -39894,7 +40014,7 @@
         <v>2026</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="n">
@@ -39904,25 +40024,25 @@
         <v>46216</v>
       </c>
       <c r="F17" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G17" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H17" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I17" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J17" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K17" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L17" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M17" t="b">
         <v>0</v>
@@ -39935,7 +40055,7 @@
         <v>50</v>
       </c>
       <c r="Q17" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -39946,7 +40066,7 @@
         <v>2026</v>
       </c>
       <c r="B18" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="n">
@@ -39956,25 +40076,25 @@
         <v>46216</v>
       </c>
       <c r="F18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G18" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H18" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I18" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J18" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K18" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M18" t="b">
         <v>0</v>
@@ -39987,7 +40107,7 @@
         <v>44</v>
       </c>
       <c r="Q18" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -39998,7 +40118,7 @@
         <v>2026</v>
       </c>
       <c r="B19" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="n">
@@ -40008,25 +40128,25 @@
         <v>46216</v>
       </c>
       <c r="F19" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G19" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H19" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I19" t="s">
+        <v>160</v>
+      </c>
+      <c r="J19" t="s">
+        <v>137</v>
+      </c>
+      <c r="K19" t="s">
+        <v>138</v>
+      </c>
+      <c r="L19" t="s">
         <v>156</v>
-      </c>
-      <c r="J19" t="s">
-        <v>133</v>
-      </c>
-      <c r="K19" t="s">
-        <v>134</v>
-      </c>
-      <c r="L19" t="s">
-        <v>152</v>
       </c>
       <c r="M19" t="b">
         <v>0</v>
@@ -40039,7 +40159,7 @@
         <v>10</v>
       </c>
       <c r="Q19" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -40050,7 +40170,7 @@
         <v>2026</v>
       </c>
       <c r="B20" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C20"/>
       <c r="D20" t="n">
@@ -40060,25 +40180,25 @@
         <v>46216</v>
       </c>
       <c r="F20" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G20" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H20" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I20" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J20" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L20" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
@@ -40091,7 +40211,7 @@
         <v>50</v>
       </c>
       <c r="Q20" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -40102,7 +40222,7 @@
         <v>2026</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C21"/>
       <c r="D21" t="n">
@@ -40112,25 +40232,25 @@
         <v>46216</v>
       </c>
       <c r="F21" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G21" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H21" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J21" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K21" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L21" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M21" t="b">
         <v>0</v>
@@ -40143,7 +40263,7 @@
         <v>2</v>
       </c>
       <c r="Q21" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -40154,7 +40274,7 @@
         <v>2026</v>
       </c>
       <c r="B22" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="n">
@@ -40164,25 +40284,25 @@
         <v>46216</v>
       </c>
       <c r="F22" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G22" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H22" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I22" t="s">
+        <v>160</v>
+      </c>
+      <c r="J22" t="s">
+        <v>137</v>
+      </c>
+      <c r="K22" t="s">
+        <v>138</v>
+      </c>
+      <c r="L22" t="s">
         <v>156</v>
-      </c>
-      <c r="J22" t="s">
-        <v>133</v>
-      </c>
-      <c r="K22" t="s">
-        <v>134</v>
-      </c>
-      <c r="L22" t="s">
-        <v>152</v>
       </c>
       <c r="M22" t="b">
         <v>0</v>
@@ -40195,7 +40315,7 @@
         <v>27</v>
       </c>
       <c r="Q22" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -40206,7 +40326,7 @@
         <v>2026</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C23"/>
       <c r="D23" t="n">
@@ -40216,25 +40336,25 @@
         <v>46216</v>
       </c>
       <c r="F23" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G23" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J23" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K23" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L23" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M23" t="b">
         <v>0</v>
@@ -40247,7 +40367,7 @@
         <v>44</v>
       </c>
       <c r="Q23" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -40258,7 +40378,7 @@
         <v>2026</v>
       </c>
       <c r="B24" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C24"/>
       <c r="D24" t="n">
@@ -40268,25 +40388,25 @@
         <v>46216</v>
       </c>
       <c r="F24" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G24" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H24" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I24" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J24" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K24" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L24" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M24" t="b">
         <v>0</v>
@@ -40299,7 +40419,7 @@
         <v>9</v>
       </c>
       <c r="Q24" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -40310,7 +40430,7 @@
         <v>2026</v>
       </c>
       <c r="B25" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C25"/>
       <c r="D25" t="n">
@@ -40320,25 +40440,25 @@
         <v>46216</v>
       </c>
       <c r="F25" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G25" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H25" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I25" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J25" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K25" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L25" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
@@ -40351,7 +40471,7 @@
         <v>28</v>
       </c>
       <c r="Q25" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -40362,7 +40482,7 @@
         <v>2026</v>
       </c>
       <c r="B26" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C26"/>
       <c r="D26" t="n">
@@ -40372,25 +40492,25 @@
         <v>46216</v>
       </c>
       <c r="F26" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G26" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H26" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I26" t="s">
+        <v>160</v>
+      </c>
+      <c r="J26" t="s">
+        <v>137</v>
+      </c>
+      <c r="K26" t="s">
+        <v>138</v>
+      </c>
+      <c r="L26" t="s">
         <v>156</v>
-      </c>
-      <c r="J26" t="s">
-        <v>133</v>
-      </c>
-      <c r="K26" t="s">
-        <v>134</v>
-      </c>
-      <c r="L26" t="s">
-        <v>152</v>
       </c>
       <c r="M26" t="b">
         <v>0</v>
@@ -40403,7 +40523,7 @@
         <v>3</v>
       </c>
       <c r="Q26" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -40414,7 +40534,7 @@
         <v>2026</v>
       </c>
       <c r="B27" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C27"/>
       <c r="D27" t="n">
@@ -40424,25 +40544,25 @@
         <v>46216</v>
       </c>
       <c r="F27" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G27" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H27" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I27" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J27" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K27" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L27" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M27" t="b">
         <v>0</v>
@@ -40455,7 +40575,7 @@
         <v>50</v>
       </c>
       <c r="Q27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -40466,7 +40586,7 @@
         <v>2026</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C28"/>
       <c r="D28" t="n">
@@ -40476,25 +40596,25 @@
         <v>46216</v>
       </c>
       <c r="F28" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G28" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H28" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I28" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J28" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L28" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M28" t="b">
         <v>0</v>
@@ -40507,7 +40627,7 @@
         <v>1</v>
       </c>
       <c r="Q28" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -40518,7 +40638,7 @@
         <v>2026</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C29"/>
       <c r="D29" t="n">
@@ -40528,25 +40648,25 @@
         <v>46216</v>
       </c>
       <c r="F29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G29" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H29" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I29" t="s">
+        <v>160</v>
+      </c>
+      <c r="J29" t="s">
+        <v>137</v>
+      </c>
+      <c r="K29" t="s">
+        <v>138</v>
+      </c>
+      <c r="L29" t="s">
         <v>156</v>
-      </c>
-      <c r="J29" t="s">
-        <v>133</v>
-      </c>
-      <c r="K29" t="s">
-        <v>134</v>
-      </c>
-      <c r="L29" t="s">
-        <v>152</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
@@ -40559,7 +40679,7 @@
         <v>12</v>
       </c>
       <c r="Q29" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -40570,7 +40690,7 @@
         <v>2026</v>
       </c>
       <c r="B30" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C30"/>
       <c r="D30" t="n">
@@ -40580,25 +40700,25 @@
         <v>46216</v>
       </c>
       <c r="F30" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G30" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H30" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I30" t="s">
+        <v>160</v>
+      </c>
+      <c r="J30" t="s">
+        <v>163</v>
+      </c>
+      <c r="K30" t="s">
+        <v>138</v>
+      </c>
+      <c r="L30" t="s">
         <v>156</v>
-      </c>
-      <c r="J30" t="s">
-        <v>159</v>
-      </c>
-      <c r="K30" t="s">
-        <v>134</v>
-      </c>
-      <c r="L30" t="s">
-        <v>152</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
@@ -40611,7 +40731,7 @@
         <v>11</v>
       </c>
       <c r="Q30" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -40622,7 +40742,7 @@
         <v>2026</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C31"/>
       <c r="D31" t="n">
@@ -40632,25 +40752,25 @@
         <v>46216</v>
       </c>
       <c r="F31" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G31" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H31" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I31" t="s">
+        <v>160</v>
+      </c>
+      <c r="J31" t="s">
+        <v>137</v>
+      </c>
+      <c r="K31" t="s">
+        <v>138</v>
+      </c>
+      <c r="L31" t="s">
         <v>156</v>
-      </c>
-      <c r="J31" t="s">
-        <v>133</v>
-      </c>
-      <c r="K31" t="s">
-        <v>134</v>
-      </c>
-      <c r="L31" t="s">
-        <v>152</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
@@ -40663,7 +40783,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -40674,7 +40794,7 @@
         <v>2026</v>
       </c>
       <c r="B32" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C32"/>
       <c r="D32" t="n">
@@ -40684,25 +40804,25 @@
         <v>46216</v>
       </c>
       <c r="F32" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G32" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H32" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I32" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J32" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K32" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L32" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
@@ -40715,7 +40835,7 @@
         <v>10</v>
       </c>
       <c r="Q32" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -40726,7 +40846,7 @@
         <v>2026</v>
       </c>
       <c r="B33" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C33"/>
       <c r="D33" t="n">
@@ -40736,25 +40856,25 @@
         <v>46216</v>
       </c>
       <c r="F33" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G33" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H33" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I33" t="s">
+        <v>160</v>
+      </c>
+      <c r="J33" t="s">
+        <v>137</v>
+      </c>
+      <c r="K33" t="s">
+        <v>138</v>
+      </c>
+      <c r="L33" t="s">
         <v>156</v>
-      </c>
-      <c r="J33" t="s">
-        <v>133</v>
-      </c>
-      <c r="K33" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" t="s">
-        <v>152</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
@@ -40767,7 +40887,7 @@
         <v>4</v>
       </c>
       <c r="Q33" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -40778,7 +40898,7 @@
         <v>2026</v>
       </c>
       <c r="B34" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C34"/>
       <c r="D34" t="n">
@@ -40788,25 +40908,25 @@
         <v>46216</v>
       </c>
       <c r="F34" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G34" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H34" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I34" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J34" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K34" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L34" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
@@ -40819,7 +40939,7 @@
         <v>10</v>
       </c>
       <c r="Q34" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -40830,7 +40950,7 @@
         <v>2026</v>
       </c>
       <c r="B35" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C35"/>
       <c r="D35" t="n">
@@ -40840,25 +40960,25 @@
         <v>46216</v>
       </c>
       <c r="F35" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G35" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H35" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I35" t="s">
+        <v>160</v>
+      </c>
+      <c r="J35" t="s">
+        <v>137</v>
+      </c>
+      <c r="K35" t="s">
+        <v>138</v>
+      </c>
+      <c r="L35" t="s">
         <v>156</v>
-      </c>
-      <c r="J35" t="s">
-        <v>133</v>
-      </c>
-      <c r="K35" t="s">
-        <v>134</v>
-      </c>
-      <c r="L35" t="s">
-        <v>152</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
@@ -40871,7 +40991,7 @@
         <v>2</v>
       </c>
       <c r="Q35" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -40882,7 +41002,7 @@
         <v>2026</v>
       </c>
       <c r="B36" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C36"/>
       <c r="D36" t="n">
@@ -40892,25 +41012,25 @@
         <v>46216</v>
       </c>
       <c r="F36" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G36" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H36" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I36" t="s">
+        <v>160</v>
+      </c>
+      <c r="J36" t="s">
+        <v>163</v>
+      </c>
+      <c r="K36" t="s">
+        <v>138</v>
+      </c>
+      <c r="L36" t="s">
         <v>156</v>
-      </c>
-      <c r="J36" t="s">
-        <v>159</v>
-      </c>
-      <c r="K36" t="s">
-        <v>134</v>
-      </c>
-      <c r="L36" t="s">
-        <v>152</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
@@ -40923,7 +41043,7 @@
         <v>41</v>
       </c>
       <c r="Q36" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -40934,7 +41054,7 @@
         <v>2026</v>
       </c>
       <c r="B37" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C37"/>
       <c r="D37" t="n">
@@ -40944,25 +41064,25 @@
         <v>46216</v>
       </c>
       <c r="F37" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G37" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H37" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I37" t="s">
+        <v>160</v>
+      </c>
+      <c r="J37" t="s">
+        <v>163</v>
+      </c>
+      <c r="K37" t="s">
+        <v>138</v>
+      </c>
+      <c r="L37" t="s">
         <v>156</v>
-      </c>
-      <c r="J37" t="s">
-        <v>159</v>
-      </c>
-      <c r="K37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L37" t="s">
-        <v>152</v>
       </c>
       <c r="M37" t="b">
         <v>0</v>
@@ -40975,7 +41095,7 @@
         <v>33</v>
       </c>
       <c r="Q37" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -40986,7 +41106,7 @@
         <v>2026</v>
       </c>
       <c r="B38" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C38"/>
       <c r="D38" t="n">
@@ -40996,25 +41116,25 @@
         <v>46217</v>
       </c>
       <c r="F38" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G38" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H38" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I38" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J38" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K38" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L38" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M38" t="b">
         <v>0</v>
@@ -41027,7 +41147,7 @@
         <v>19</v>
       </c>
       <c r="Q38" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -41038,7 +41158,7 @@
         <v>2026</v>
       </c>
       <c r="B39" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C39"/>
       <c r="D39" t="n">
@@ -41048,25 +41168,25 @@
         <v>46217</v>
       </c>
       <c r="F39" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G39" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H39" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I39" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L39" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
@@ -41079,7 +41199,7 @@
         <v>36</v>
       </c>
       <c r="Q39" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -41090,7 +41210,7 @@
         <v>2026</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C40"/>
       <c r="D40" t="n">
@@ -41100,25 +41220,25 @@
         <v>46217</v>
       </c>
       <c r="F40" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G40" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H40" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I40" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J40" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K40" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L40" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
@@ -41131,7 +41251,7 @@
         <v>2</v>
       </c>
       <c r="Q40" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -41142,7 +41262,7 @@
         <v>2026</v>
       </c>
       <c r="B41" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C41"/>
       <c r="D41" t="n">
@@ -41152,25 +41272,25 @@
         <v>46217</v>
       </c>
       <c r="F41" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G41" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H41" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I41" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J41" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K41" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L41" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
@@ -41183,7 +41303,7 @@
         <v>36</v>
       </c>
       <c r="Q41" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -41194,7 +41314,7 @@
         <v>2026</v>
       </c>
       <c r="B42" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C42"/>
       <c r="D42" t="n">
@@ -41204,25 +41324,25 @@
         <v>46217</v>
       </c>
       <c r="F42" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H42" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I42" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J42" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K42" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L42" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
@@ -41235,7 +41355,7 @@
         <v>1</v>
       </c>
       <c r="Q42" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -41246,7 +41366,7 @@
         <v>2026</v>
       </c>
       <c r="B43" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C43"/>
       <c r="D43" t="n">
@@ -41256,25 +41376,25 @@
         <v>46217</v>
       </c>
       <c r="F43" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G43" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H43" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I43" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J43" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K43" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L43" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M43" t="b">
         <v>0</v>
@@ -41287,7 +41407,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -41298,7 +41418,7 @@
         <v>2026</v>
       </c>
       <c r="B44" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C44"/>
       <c r="D44" t="n">
@@ -41308,25 +41428,25 @@
         <v>46217</v>
       </c>
       <c r="F44" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G44" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H44" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I44" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J44" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K44" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L44" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
@@ -41339,7 +41459,7 @@
         <v>4</v>
       </c>
       <c r="Q44" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -41350,7 +41470,7 @@
         <v>2026</v>
       </c>
       <c r="B45" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C45"/>
       <c r="D45" t="n">
@@ -41360,25 +41480,25 @@
         <v>46217</v>
       </c>
       <c r="F45" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G45" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H45" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I45" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J45" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K45" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L45" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
@@ -41391,7 +41511,7 @@
         <v>2</v>
       </c>
       <c r="Q45" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -41402,7 +41522,7 @@
         <v>2026</v>
       </c>
       <c r="B46" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C46"/>
       <c r="D46" t="n">
@@ -41412,25 +41532,25 @@
         <v>46217</v>
       </c>
       <c r="F46" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G46" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H46" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I46" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J46" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L46" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
@@ -41443,7 +41563,7 @@
         <v>8</v>
       </c>
       <c r="Q46" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -41454,7 +41574,7 @@
         <v>2026</v>
       </c>
       <c r="B47" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C47"/>
       <c r="D47" t="n">
@@ -41464,25 +41584,25 @@
         <v>46217</v>
       </c>
       <c r="F47" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G47" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H47" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I47" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J47" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K47" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L47" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
@@ -41495,7 +41615,7 @@
         <v>5</v>
       </c>
       <c r="Q47" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -41506,7 +41626,7 @@
         <v>2026</v>
       </c>
       <c r="B48" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C48"/>
       <c r="D48" t="n">
@@ -41516,25 +41636,25 @@
         <v>46217</v>
       </c>
       <c r="F48" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G48" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H48" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I48" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J48" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K48" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L48" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
@@ -41547,7 +41667,7 @@
         <v>36</v>
       </c>
       <c r="Q48" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -41558,7 +41678,7 @@
         <v>2026</v>
       </c>
       <c r="B49" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C49"/>
       <c r="D49" t="n">
@@ -41568,25 +41688,25 @@
         <v>46217</v>
       </c>
       <c r="F49" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G49" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H49" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I49" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J49" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K49" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L49" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -41599,7 +41719,7 @@
         <v>8</v>
       </c>
       <c r="Q49" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -41610,7 +41730,7 @@
         <v>2026</v>
       </c>
       <c r="B50" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C50"/>
       <c r="D50" t="n">
@@ -41620,25 +41740,25 @@
         <v>46217</v>
       </c>
       <c r="F50" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G50" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H50" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I50" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J50" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K50" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L50" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -41651,7 +41771,7 @@
         <v>7</v>
       </c>
       <c r="Q50" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -41662,7 +41782,7 @@
         <v>2026</v>
       </c>
       <c r="B51" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C51"/>
       <c r="D51" t="n">
@@ -41672,25 +41792,25 @@
         <v>46217</v>
       </c>
       <c r="F51" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G51" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H51" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I51" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J51" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K51" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L51" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -41703,7 +41823,7 @@
         <v>1</v>
       </c>
       <c r="Q51" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -41714,7 +41834,7 @@
         <v>2026</v>
       </c>
       <c r="B52" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C52"/>
       <c r="D52" t="n">
@@ -41724,25 +41844,25 @@
         <v>46217</v>
       </c>
       <c r="F52" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G52" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H52" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I52" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J52" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K52" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L52" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
@@ -41755,7 +41875,7 @@
         <v>4</v>
       </c>
       <c r="Q52" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -41766,7 +41886,7 @@
         <v>2026</v>
       </c>
       <c r="B53" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C53"/>
       <c r="D53" t="n">
@@ -41776,25 +41896,25 @@
         <v>46217</v>
       </c>
       <c r="F53" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G53" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H53" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I53" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J53" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K53" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L53" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
@@ -41807,7 +41927,7 @@
         <v>4</v>
       </c>
       <c r="Q53" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -41818,7 +41938,7 @@
         <v>2026</v>
       </c>
       <c r="B54" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C54"/>
       <c r="D54" t="n">
@@ -41828,25 +41948,25 @@
         <v>46217</v>
       </c>
       <c r="F54" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G54" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H54" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I54" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J54" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K54" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L54" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -41859,7 +41979,7 @@
         <v>1</v>
       </c>
       <c r="Q54" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -41870,7 +41990,7 @@
         <v>2026</v>
       </c>
       <c r="B55" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C55"/>
       <c r="D55" t="n">
@@ -41880,25 +42000,25 @@
         <v>46217</v>
       </c>
       <c r="F55" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G55" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H55" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I55" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J55" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K55" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L55" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -41911,7 +42031,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -41922,7 +42042,7 @@
         <v>2026</v>
       </c>
       <c r="B56" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C56"/>
       <c r="D56" t="n">
@@ -41932,25 +42052,25 @@
         <v>46217</v>
       </c>
       <c r="F56" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G56" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H56" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I56" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J56" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K56" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L56" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
@@ -41963,7 +42083,7 @@
         <v>1</v>
       </c>
       <c r="Q56" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -41974,7 +42094,7 @@
         <v>2026</v>
       </c>
       <c r="B57" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C57"/>
       <c r="D57" t="n">
@@ -41984,25 +42104,25 @@
         <v>46217</v>
       </c>
       <c r="F57" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G57" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H57" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I57" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J57" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K57" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L57" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
@@ -42015,7 +42135,7 @@
         <v>17</v>
       </c>
       <c r="Q57" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -42026,7 +42146,7 @@
         <v>2026</v>
       </c>
       <c r="B58" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C58"/>
       <c r="D58" t="n">
@@ -42036,25 +42156,25 @@
         <v>46217</v>
       </c>
       <c r="F58" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G58" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H58" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I58" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J58" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K58" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L58" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -42067,7 +42187,7 @@
         <v>2</v>
       </c>
       <c r="Q58" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -42078,7 +42198,7 @@
         <v>2026</v>
       </c>
       <c r="B59" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C59"/>
       <c r="D59" t="n">
@@ -42088,25 +42208,25 @@
         <v>46217</v>
       </c>
       <c r="F59" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G59" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H59" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I59" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J59" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K59" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L59" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -42119,7 +42239,7 @@
         <v>16</v>
       </c>
       <c r="Q59" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -42130,7 +42250,7 @@
         <v>2026</v>
       </c>
       <c r="B60" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C60"/>
       <c r="D60" t="n">
@@ -42140,25 +42260,25 @@
         <v>46217</v>
       </c>
       <c r="F60" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G60" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H60" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I60" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J60" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K60" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L60" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -42171,7 +42291,7 @@
         <v>1</v>
       </c>
       <c r="Q60" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -42182,7 +42302,7 @@
         <v>2026</v>
       </c>
       <c r="B61" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C61"/>
       <c r="D61" t="n">
@@ -42192,25 +42312,25 @@
         <v>46217</v>
       </c>
       <c r="F61" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G61" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H61" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I61" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J61" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K61" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L61" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -42223,7 +42343,7 @@
         <v>19</v>
       </c>
       <c r="Q61" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -42234,7 +42354,7 @@
         <v>2026</v>
       </c>
       <c r="B62" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C62"/>
       <c r="D62" t="n">
@@ -42244,25 +42364,25 @@
         <v>46217</v>
       </c>
       <c r="F62" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G62" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H62" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I62" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J62" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K62" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L62" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
@@ -42275,7 +42395,7 @@
         <v>1</v>
       </c>
       <c r="Q62" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -42286,7 +42406,7 @@
         <v>2026</v>
       </c>
       <c r="B63" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C63"/>
       <c r="D63" t="n">
@@ -42296,25 +42416,25 @@
         <v>46217</v>
       </c>
       <c r="F63" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G63" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H63" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I63" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J63" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K63" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L63" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -42327,7 +42447,7 @@
         <v>31</v>
       </c>
       <c r="Q63" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -42338,7 +42458,7 @@
         <v>2026</v>
       </c>
       <c r="B64" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C64"/>
       <c r="D64" t="n">
@@ -42348,25 +42468,25 @@
         <v>46217</v>
       </c>
       <c r="F64" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G64" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H64" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I64" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J64" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K64" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L64" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
@@ -42379,7 +42499,7 @@
         <v>8</v>
       </c>
       <c r="Q64" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -42390,7 +42510,7 @@
         <v>2026</v>
       </c>
       <c r="B65" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C65"/>
       <c r="D65" t="n">
@@ -42400,25 +42520,25 @@
         <v>46217</v>
       </c>
       <c r="F65" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G65" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H65" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I65" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J65" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K65" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L65" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
@@ -42431,7 +42551,7 @@
         <v>25</v>
       </c>
       <c r="Q65" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -42442,7 +42562,7 @@
         <v>2026</v>
       </c>
       <c r="B66" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C66"/>
       <c r="D66" t="n">
@@ -42452,25 +42572,25 @@
         <v>46217</v>
       </c>
       <c r="F66" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G66" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H66" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I66" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J66" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K66" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L66" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -42483,7 +42603,7 @@
         <v>32</v>
       </c>
       <c r="Q66" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -42494,7 +42614,7 @@
         <v>2026</v>
       </c>
       <c r="B67" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C67"/>
       <c r="D67" t="n">
@@ -42504,25 +42624,25 @@
         <v>46217</v>
       </c>
       <c r="F67" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G67" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H67" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I67" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J67" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K67" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L67" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -42535,7 +42655,7 @@
         <v>7</v>
       </c>
       <c r="Q67" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -42546,7 +42666,7 @@
         <v>2026</v>
       </c>
       <c r="B68" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C68"/>
       <c r="D68" t="n">
@@ -42556,25 +42676,25 @@
         <v>46217</v>
       </c>
       <c r="F68" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G68" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H68" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I68" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J68" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K68" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L68" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -42587,7 +42707,7 @@
         <v>18</v>
       </c>
       <c r="Q68" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -42598,7 +42718,7 @@
         <v>2026</v>
       </c>
       <c r="B69" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C69"/>
       <c r="D69" t="n">
@@ -42608,25 +42728,25 @@
         <v>46218</v>
       </c>
       <c r="F69" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G69" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H69" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I69" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J69" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K69" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L69" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -42639,7 +42759,7 @@
         <v>50</v>
       </c>
       <c r="Q69" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -42650,7 +42770,7 @@
         <v>2026</v>
       </c>
       <c r="B70" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C70"/>
       <c r="D70" t="n">
@@ -42660,25 +42780,25 @@
         <v>46218</v>
       </c>
       <c r="F70" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G70" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H70" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I70" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J70" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K70" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L70" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -42691,7 +42811,7 @@
         <v>9</v>
       </c>
       <c r="Q70" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -42702,7 +42822,7 @@
         <v>2026</v>
       </c>
       <c r="B71" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C71"/>
       <c r="D71" t="n">
@@ -42712,25 +42832,25 @@
         <v>46218</v>
       </c>
       <c r="F71" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G71" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H71" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I71" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J71" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K71" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L71" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -42743,7 +42863,7 @@
         <v>7</v>
       </c>
       <c r="Q71" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -42754,7 +42874,7 @@
         <v>2026</v>
       </c>
       <c r="B72" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C72"/>
       <c r="D72" t="n">
@@ -42764,25 +42884,25 @@
         <v>46218</v>
       </c>
       <c r="F72" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G72" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H72" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I72" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J72" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K72" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L72" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -42795,7 +42915,7 @@
         <v>7</v>
       </c>
       <c r="Q72" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -42806,7 +42926,7 @@
         <v>2026</v>
       </c>
       <c r="B73" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C73"/>
       <c r="D73" t="n">
@@ -42816,25 +42936,25 @@
         <v>46218</v>
       </c>
       <c r="F73" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G73" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H73" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I73" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J73" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K73" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L73" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -42847,7 +42967,7 @@
         <v>50</v>
       </c>
       <c r="Q73" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -42858,7 +42978,7 @@
         <v>2026</v>
       </c>
       <c r="B74" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C74"/>
       <c r="D74" t="n">
@@ -42868,25 +42988,25 @@
         <v>46218</v>
       </c>
       <c r="F74" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G74" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H74" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I74" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J74" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K74" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L74" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -42899,7 +43019,7 @@
         <v>23</v>
       </c>
       <c r="Q74" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -42910,7 +43030,7 @@
         <v>2026</v>
       </c>
       <c r="B75" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C75"/>
       <c r="D75" t="n">
@@ -42920,25 +43040,25 @@
         <v>46218</v>
       </c>
       <c r="F75" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G75" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H75" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I75" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J75" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K75" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L75" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -42951,7 +43071,7 @@
         <v>8</v>
       </c>
       <c r="Q75" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -42962,7 +43082,7 @@
         <v>2026</v>
       </c>
       <c r="B76" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C76"/>
       <c r="D76" t="n">
@@ -42972,25 +43092,25 @@
         <v>46218</v>
       </c>
       <c r="F76" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G76" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H76" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I76" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J76" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K76" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L76" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -43003,7 +43123,7 @@
         <v>19</v>
       </c>
       <c r="Q76" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -43014,7 +43134,7 @@
         <v>2026</v>
       </c>
       <c r="B77" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C77"/>
       <c r="D77" t="n">
@@ -43024,25 +43144,25 @@
         <v>46218</v>
       </c>
       <c r="F77" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G77" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H77" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I77" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J77" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K77" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L77" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -43055,7 +43175,7 @@
         <v>49</v>
       </c>
       <c r="Q77" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -43066,7 +43186,7 @@
         <v>2026</v>
       </c>
       <c r="B78" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C78"/>
       <c r="D78" t="n">
@@ -43076,25 +43196,25 @@
         <v>46218</v>
       </c>
       <c r="F78" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G78" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H78" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I78" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J78" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K78" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L78" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -43107,7 +43227,7 @@
         <v>7</v>
       </c>
       <c r="Q78" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -43118,7 +43238,7 @@
         <v>2026</v>
       </c>
       <c r="B79" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C79"/>
       <c r="D79" t="n">
@@ -43128,25 +43248,25 @@
         <v>46218</v>
       </c>
       <c r="F79" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G79" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H79" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I79" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J79" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K79" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L79" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -43159,7 +43279,7 @@
         <v>8</v>
       </c>
       <c r="Q79" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -43170,7 +43290,7 @@
         <v>2026</v>
       </c>
       <c r="B80" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C80"/>
       <c r="D80" t="n">
@@ -43180,25 +43300,25 @@
         <v>46218</v>
       </c>
       <c r="F80" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G80" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H80" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I80" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J80" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K80" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L80" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -43211,7 +43331,7 @@
         <v>2</v>
       </c>
       <c r="Q80" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -43222,7 +43342,7 @@
         <v>2026</v>
       </c>
       <c r="B81" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C81"/>
       <c r="D81" t="n">
@@ -43232,25 +43352,25 @@
         <v>46218</v>
       </c>
       <c r="F81" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G81" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H81" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I81" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J81" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K81" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L81" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -43263,7 +43383,7 @@
         <v>22</v>
       </c>
       <c r="Q81" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
@@ -43274,7 +43394,7 @@
         <v>2026</v>
       </c>
       <c r="B82" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C82"/>
       <c r="D82" t="n">
@@ -43284,25 +43404,25 @@
         <v>46218</v>
       </c>
       <c r="F82" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G82" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H82" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I82" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J82" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K82" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L82" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -43315,7 +43435,7 @@
         <v>7</v>
       </c>
       <c r="Q82" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -43326,7 +43446,7 @@
         <v>2026</v>
       </c>
       <c r="B83" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C83"/>
       <c r="D83" t="n">
@@ -43336,25 +43456,25 @@
         <v>46218</v>
       </c>
       <c r="F83" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G83" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H83" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I83" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J83" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K83" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L83" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -43367,7 +43487,7 @@
         <v>5</v>
       </c>
       <c r="Q83" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -43378,7 +43498,7 @@
         <v>2026</v>
       </c>
       <c r="B84" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C84"/>
       <c r="D84" t="n">
@@ -43388,25 +43508,25 @@
         <v>46218</v>
       </c>
       <c r="F84" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G84" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H84" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I84" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J84" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K84" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L84" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -43419,7 +43539,7 @@
         <v>1</v>
       </c>
       <c r="Q84" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -43430,7 +43550,7 @@
         <v>2026</v>
       </c>
       <c r="B85" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C85"/>
       <c r="D85" t="n">
@@ -43440,25 +43560,25 @@
         <v>46218</v>
       </c>
       <c r="F85" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G85" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H85" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="I85" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J85" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K85" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L85" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -43471,7 +43591,7 @@
         <v>10</v>
       </c>
       <c r="Q85" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
@@ -43482,7 +43602,7 @@
         <v>2026</v>
       </c>
       <c r="B86" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C86"/>
       <c r="D86" t="n">
@@ -43492,25 +43612,25 @@
         <v>46218</v>
       </c>
       <c r="F86" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G86" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H86" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I86" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J86" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K86" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L86" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -43523,7 +43643,7 @@
         <v>3</v>
       </c>
       <c r="Q86" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -43534,7 +43654,7 @@
         <v>2026</v>
       </c>
       <c r="B87" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C87"/>
       <c r="D87" t="n">
@@ -43544,25 +43664,25 @@
         <v>46218</v>
       </c>
       <c r="F87" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G87" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H87" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I87" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J87" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K87" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L87" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -43575,7 +43695,7 @@
         <v>1</v>
       </c>
       <c r="Q87" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -43586,7 +43706,7 @@
         <v>2026</v>
       </c>
       <c r="B88" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C88"/>
       <c r="D88" t="n">
@@ -43596,25 +43716,25 @@
         <v>46218</v>
       </c>
       <c r="F88" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G88" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H88" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="I88" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J88" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K88" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L88" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -43627,7 +43747,7 @@
         <v>2</v>
       </c>
       <c r="Q88" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
@@ -43638,7 +43758,7 @@
         <v>2026</v>
       </c>
       <c r="B89" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C89"/>
       <c r="D89" t="n">
@@ -43648,25 +43768,25 @@
         <v>46218</v>
       </c>
       <c r="F89" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G89" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H89" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I89" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J89" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K89" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L89" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -43679,7 +43799,7 @@
         <v>5</v>
       </c>
       <c r="Q89" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -43690,7 +43810,7 @@
         <v>2026</v>
       </c>
       <c r="B90" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C90"/>
       <c r="D90" t="n">
@@ -43700,25 +43820,25 @@
         <v>46218</v>
       </c>
       <c r="F90" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G90" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H90" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="I90" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J90" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K90" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L90" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -43731,7 +43851,7 @@
         <v>5</v>
       </c>
       <c r="Q90" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -43742,7 +43862,7 @@
         <v>2026</v>
       </c>
       <c r="B91" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C91"/>
       <c r="D91" t="n">
@@ -43752,25 +43872,25 @@
         <v>46218</v>
       </c>
       <c r="F91" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G91" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H91" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="I91" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J91" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K91" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L91" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -43783,7 +43903,7 @@
         <v>1</v>
       </c>
       <c r="Q91" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -43794,7 +43914,7 @@
         <v>2026</v>
       </c>
       <c r="B92" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C92"/>
       <c r="D92" t="n">
@@ -43804,25 +43924,25 @@
         <v>46218</v>
       </c>
       <c r="F92" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G92" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H92" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="I92" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J92" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K92" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L92" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -43835,7 +43955,7 @@
         <v>4</v>
       </c>
       <c r="Q92" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -43846,7 +43966,7 @@
         <v>2026</v>
       </c>
       <c r="B93" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C93"/>
       <c r="D93" t="n">
@@ -43856,25 +43976,25 @@
         <v>46218</v>
       </c>
       <c r="F93" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G93" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H93" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="I93" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J93" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K93" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L93" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -43887,7 +44007,7 @@
         <v>1</v>
       </c>
       <c r="Q93" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
@@ -43898,7 +44018,7 @@
         <v>2026</v>
       </c>
       <c r="B94" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C94"/>
       <c r="D94" t="n">
@@ -43908,25 +44028,25 @@
         <v>46218</v>
       </c>
       <c r="F94" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G94" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H94" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I94" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J94" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K94" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L94" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -43939,7 +44059,7 @@
         <v>25</v>
       </c>
       <c r="Q94" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -43950,7 +44070,7 @@
         <v>2026</v>
       </c>
       <c r="B95" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C95"/>
       <c r="D95" t="n">
@@ -43960,25 +44080,25 @@
         <v>46218</v>
       </c>
       <c r="F95" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G95" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H95" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="I95" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J95" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K95" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L95" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -43991,7 +44111,7 @@
         <v>9</v>
       </c>
       <c r="Q95" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
@@ -44002,7 +44122,7 @@
         <v>2026</v>
       </c>
       <c r="B96" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C96"/>
       <c r="D96" t="n">
@@ -44012,25 +44132,25 @@
         <v>46218</v>
       </c>
       <c r="F96" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G96" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H96" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="I96" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J96" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K96" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L96" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -44043,7 +44163,7 @@
         <v>8</v>
       </c>
       <c r="Q96" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
@@ -44054,7 +44174,7 @@
         <v>2026</v>
       </c>
       <c r="B97" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C97"/>
       <c r="D97" t="n">
@@ -44064,25 +44184,25 @@
         <v>46218</v>
       </c>
       <c r="F97" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G97" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H97" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I97" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J97" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K97" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L97" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -44095,7 +44215,7 @@
         <v>20</v>
       </c>
       <c r="Q97" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
@@ -44106,7 +44226,7 @@
         <v>2026</v>
       </c>
       <c r="B98" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C98"/>
       <c r="D98" t="n">
@@ -44116,25 +44236,25 @@
         <v>46218</v>
       </c>
       <c r="F98" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G98" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H98" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I98" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J98" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K98" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L98" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
@@ -44147,7 +44267,7 @@
         <v>11</v>
       </c>
       <c r="Q98" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
@@ -44158,7 +44278,7 @@
         <v>2026</v>
       </c>
       <c r="B99" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C99"/>
       <c r="D99" t="n">
@@ -44168,25 +44288,25 @@
         <v>46218</v>
       </c>
       <c r="F99" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G99" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H99" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I99" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J99" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K99" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L99" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -44199,7 +44319,7 @@
         <v>2</v>
       </c>
       <c r="Q99" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -44210,7 +44330,7 @@
         <v>2026</v>
       </c>
       <c r="B100" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C100"/>
       <c r="D100" t="n">
@@ -44220,25 +44340,25 @@
         <v>46218</v>
       </c>
       <c r="F100" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G100" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H100" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I100" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J100" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K100" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L100" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
@@ -44251,7 +44371,7 @@
         <v>39</v>
       </c>
       <c r="Q100" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
@@ -44262,7 +44382,7 @@
         <v>2026</v>
       </c>
       <c r="B101" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C101"/>
       <c r="D101" t="n">
@@ -44272,25 +44392,25 @@
         <v>46218</v>
       </c>
       <c r="F101" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G101" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H101" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I101" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J101" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K101" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L101" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M101" t="b">
         <v>0</v>
@@ -44303,7 +44423,7 @@
         <v>6</v>
       </c>
       <c r="Q101" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -44314,7 +44434,7 @@
         <v>2026</v>
       </c>
       <c r="B102" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C102"/>
       <c r="D102" t="n">
@@ -44324,25 +44444,25 @@
         <v>46218</v>
       </c>
       <c r="F102" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G102" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H102" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I102" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J102" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K102" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L102" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
@@ -44355,7 +44475,7 @@
         <v>9</v>
       </c>
       <c r="Q102" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
@@ -44366,7 +44486,7 @@
         <v>2026</v>
       </c>
       <c r="B103" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C103"/>
       <c r="D103" t="n">
@@ -44376,25 +44496,25 @@
         <v>46218</v>
       </c>
       <c r="F103" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G103" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H103" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I103" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J103" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K103" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L103" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M103" t="b">
         <v>0</v>
@@ -44407,7 +44527,7 @@
         <v>6</v>
       </c>
       <c r="Q103" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
@@ -44418,7 +44538,7 @@
         <v>2026</v>
       </c>
       <c r="B104" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C104"/>
       <c r="D104" t="n">
@@ -44428,25 +44548,25 @@
         <v>46218</v>
       </c>
       <c r="F104" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G104" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H104" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="I104" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J104" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K104" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L104" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
@@ -44459,7 +44579,7 @@
         <v>2</v>
       </c>
       <c r="Q104" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
@@ -44470,7 +44590,7 @@
         <v>2026</v>
       </c>
       <c r="B105" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C105"/>
       <c r="D105" t="n">
@@ -44480,25 +44600,25 @@
         <v>46218</v>
       </c>
       <c r="F105" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G105" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H105" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="I105" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J105" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K105" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L105" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -44511,7 +44631,7 @@
         <v>1</v>
       </c>
       <c r="Q105" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
@@ -44522,7 +44642,7 @@
         <v>2026</v>
       </c>
       <c r="B106" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C106"/>
       <c r="D106" t="n">
@@ -44532,25 +44652,25 @@
         <v>46219</v>
       </c>
       <c r="F106" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G106" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H106" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="I106" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J106" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K106" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L106" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M106" t="b">
         <v>0</v>
@@ -44563,7 +44683,7 @@
         <v>1</v>
       </c>
       <c r="Q106" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
@@ -44574,7 +44694,7 @@
         <v>2026</v>
       </c>
       <c r="B107" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C107"/>
       <c r="D107" t="n">
@@ -44584,25 +44704,25 @@
         <v>46219</v>
       </c>
       <c r="F107" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G107" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H107" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="I107" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J107" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K107" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L107" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M107" t="b">
         <v>0</v>
@@ -44615,7 +44735,7 @@
         <v>20</v>
       </c>
       <c r="Q107" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -44626,7 +44746,7 @@
         <v>2026</v>
       </c>
       <c r="B108" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C108"/>
       <c r="D108" t="n">
@@ -44636,25 +44756,25 @@
         <v>46219</v>
       </c>
       <c r="F108" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G108" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H108" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="I108" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J108" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K108" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L108" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M108" t="b">
         <v>0</v>
@@ -44667,7 +44787,7 @@
         <v>2</v>
       </c>
       <c r="Q108" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
@@ -44678,7 +44798,7 @@
         <v>2026</v>
       </c>
       <c r="B109" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C109"/>
       <c r="D109" t="n">
@@ -44688,25 +44808,25 @@
         <v>46219</v>
       </c>
       <c r="F109" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G109" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H109" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I109" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J109" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K109" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L109" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M109" t="b">
         <v>0</v>
@@ -44719,7 +44839,7 @@
         <v>2</v>
       </c>
       <c r="Q109" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -44730,7 +44850,7 @@
         <v>2026</v>
       </c>
       <c r="B110" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C110"/>
       <c r="D110" t="n">
@@ -44740,25 +44860,25 @@
         <v>46219</v>
       </c>
       <c r="F110" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G110" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H110" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="I110" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J110" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K110" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L110" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M110" t="b">
         <v>0</v>
@@ -44771,7 +44891,7 @@
         <v>13</v>
       </c>
       <c r="Q110" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -44782,7 +44902,7 @@
         <v>2026</v>
       </c>
       <c r="B111" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C111"/>
       <c r="D111" t="n">
@@ -44792,25 +44912,25 @@
         <v>46219</v>
       </c>
       <c r="F111" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G111" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H111" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I111" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J111" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K111" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L111" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M111" t="b">
         <v>0</v>
@@ -44823,7 +44943,7 @@
         <v>50</v>
       </c>
       <c r="Q111" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -44834,7 +44954,7 @@
         <v>2026</v>
       </c>
       <c r="B112" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C112"/>
       <c r="D112" t="n">
@@ -44844,25 +44964,25 @@
         <v>46219</v>
       </c>
       <c r="F112" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G112" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H112" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I112" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J112" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K112" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L112" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M112" t="b">
         <v>0</v>
@@ -44875,7 +44995,7 @@
         <v>40</v>
       </c>
       <c r="Q112" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
@@ -44886,7 +45006,7 @@
         <v>2026</v>
       </c>
       <c r="B113" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C113"/>
       <c r="D113" t="n">
@@ -44896,25 +45016,25 @@
         <v>46219</v>
       </c>
       <c r="F113" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G113" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H113" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I113" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J113" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K113" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L113" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M113" t="b">
         <v>0</v>
@@ -44927,7 +45047,7 @@
         <v>2</v>
       </c>
       <c r="Q113" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -44938,7 +45058,7 @@
         <v>2026</v>
       </c>
       <c r="B114" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C114"/>
       <c r="D114" t="n">
@@ -44948,25 +45068,25 @@
         <v>46219</v>
       </c>
       <c r="F114" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G114" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H114" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I114" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J114" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K114" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L114" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M114" t="b">
         <v>0</v>
@@ -44979,7 +45099,7 @@
         <v>5</v>
       </c>
       <c r="Q114" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -44990,7 +45110,7 @@
         <v>2026</v>
       </c>
       <c r="B115" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C115"/>
       <c r="D115" t="n">
@@ -45000,25 +45120,25 @@
         <v>46219</v>
       </c>
       <c r="F115" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G115" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H115" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="I115" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J115" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K115" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L115" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M115" t="b">
         <v>0</v>
@@ -45031,7 +45151,7 @@
         <v>2</v>
       </c>
       <c r="Q115" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -45042,7 +45162,7 @@
         <v>2026</v>
       </c>
       <c r="B116" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C116"/>
       <c r="D116" t="n">
@@ -45052,25 +45172,25 @@
         <v>46219</v>
       </c>
       <c r="F116" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G116" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H116" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I116" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J116" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K116" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L116" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M116" t="b">
         <v>0</v>
@@ -45083,7 +45203,7 @@
         <v>29</v>
       </c>
       <c r="Q116" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
@@ -45094,7 +45214,7 @@
         <v>2026</v>
       </c>
       <c r="B117" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C117"/>
       <c r="D117" t="n">
@@ -45104,25 +45224,25 @@
         <v>46219</v>
       </c>
       <c r="F117" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G117" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H117" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I117" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J117" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K117" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L117" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M117" t="b">
         <v>0</v>
@@ -45135,7 +45255,7 @@
         <v>50</v>
       </c>
       <c r="Q117" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
@@ -45146,7 +45266,7 @@
         <v>2026</v>
       </c>
       <c r="B118" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C118"/>
       <c r="D118" t="n">
@@ -45156,25 +45276,25 @@
         <v>46219</v>
       </c>
       <c r="F118" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G118" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H118" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I118" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J118" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K118" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L118" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M118" t="b">
         <v>0</v>
@@ -45187,7 +45307,7 @@
         <v>5</v>
       </c>
       <c r="Q118" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
@@ -45198,7 +45318,7 @@
         <v>2026</v>
       </c>
       <c r="B119" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C119"/>
       <c r="D119" t="n">
@@ -45208,25 +45328,25 @@
         <v>46219</v>
       </c>
       <c r="F119" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G119" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H119" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I119" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J119" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K119" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L119" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M119" t="b">
         <v>0</v>
@@ -45239,7 +45359,7 @@
         <v>7</v>
       </c>
       <c r="Q119" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
@@ -45250,7 +45370,7 @@
         <v>2026</v>
       </c>
       <c r="B120" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C120"/>
       <c r="D120" t="n">
@@ -45260,25 +45380,25 @@
         <v>46219</v>
       </c>
       <c r="F120" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G120" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H120" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="I120" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J120" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K120" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L120" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M120" t="b">
         <v>0</v>
@@ -45291,7 +45411,7 @@
         <v>45</v>
       </c>
       <c r="Q120" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
@@ -45302,7 +45422,7 @@
         <v>2026</v>
       </c>
       <c r="B121" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C121"/>
       <c r="D121" t="n">
@@ -45312,25 +45432,25 @@
         <v>46219</v>
       </c>
       <c r="F121" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G121" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H121" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="I121" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J121" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K121" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L121" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M121" t="b">
         <v>0</v>
@@ -45343,7 +45463,7 @@
         <v>4</v>
       </c>
       <c r="Q121" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R121" t="n">
         <v>0</v>
@@ -45354,7 +45474,7 @@
         <v>2026</v>
       </c>
       <c r="B122" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C122"/>
       <c r="D122" t="n">
@@ -45364,25 +45484,25 @@
         <v>46219</v>
       </c>
       <c r="F122" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G122" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H122" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I122" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J122" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K122" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L122" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M122" t="b">
         <v>0</v>
@@ -45395,7 +45515,7 @@
         <v>1</v>
       </c>
       <c r="Q122" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R122" t="n">
         <v>0</v>
@@ -45406,7 +45526,7 @@
         <v>2026</v>
       </c>
       <c r="B123" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C123"/>
       <c r="D123" t="n">
@@ -45416,25 +45536,25 @@
         <v>46219</v>
       </c>
       <c r="F123" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G123" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H123" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I123" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J123" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K123" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L123" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M123" t="b">
         <v>0</v>
@@ -45447,7 +45567,7 @@
         <v>50</v>
       </c>
       <c r="Q123" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R123" t="n">
         <v>0</v>
@@ -45458,7 +45578,7 @@
         <v>2026</v>
       </c>
       <c r="B124" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C124"/>
       <c r="D124" t="n">
@@ -45468,25 +45588,25 @@
         <v>46219</v>
       </c>
       <c r="F124" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G124" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H124" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I124" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J124" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K124" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L124" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M124" t="b">
         <v>0</v>
@@ -45499,7 +45619,7 @@
         <v>39</v>
       </c>
       <c r="Q124" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
@@ -45518,97 +45638,137 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2"/>
-      <c r="C2"/>
+        <v>180</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15.6667</v>
+      </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3"/>
-      <c r="C3"/>
+        <v>160</v>
+      </c>
+      <c r="B3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>28.7</v>
+      </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4"/>
-      <c r="C4"/>
+        <v>213</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.7333</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15.4</v>
+      </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B5"/>
-      <c r="C5"/>
+        <v>271</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2.1111</v>
+      </c>
+      <c r="C5" t="n">
+        <v>22.5556</v>
+      </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B6" t="n">
         <v>3.5116</v>
@@ -45644,7 +45804,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B8" t="n">
         <v>0.8333</v>
@@ -45670,7 +45830,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B9" t="n">
         <v>2.3</v>
@@ -45696,7 +45856,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B10" t="n">
         <v>4.4783</v>
@@ -45733,46 +45893,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="G1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="H1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="I1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="K1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="L1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="M1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="N1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
@@ -46044,25 +46204,25 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
         <v>0.24</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
         <v>0.44</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
         <v>0.46</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I8" t="n">
         <v>0.26</v>
@@ -46448,81 +46608,137 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="H1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
+        <v>180</v>
+      </c>
+      <c r="B2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C2" t="n">
+        <v>141</v>
+      </c>
+      <c r="D2" t="n">
+        <v>168</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="H2" t="n">
+        <v>18.67</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
+        <v>160</v>
+      </c>
+      <c r="B3" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3" t="n">
+        <v>287</v>
+      </c>
+      <c r="D3" t="n">
+        <v>351</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>35.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
+        <v>213</v>
+      </c>
+      <c r="B4" t="n">
+        <v>41</v>
+      </c>
+      <c r="C4" t="n">
+        <v>231</v>
+      </c>
+      <c r="D4" t="n">
+        <v>272</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18.13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
+        <v>271</v>
+      </c>
+      <c r="B5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C5" t="n">
+        <v>203</v>
+      </c>
+      <c r="D5" t="n">
+        <v>222</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="H5" t="n">
+        <v>24.67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B6" t="n">
         <v>151</v>
@@ -46558,7 +46774,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B8" t="n">
         <v>5</v>
@@ -46584,7 +46800,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B9" t="n">
         <v>23</v>
@@ -46610,7 +46826,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B10" t="n">
         <v>103</v>
@@ -46647,46 +46863,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="I1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="J1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="M1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="N1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2">
@@ -46958,43 +47174,43 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
         <v>92.44</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="E8" t="n">
         <v>182.39</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="G8" t="n">
         <v>160.99</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="I8" t="n">
         <v>79.76</v>
       </c>
       <c r="J8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K8" t="n">
         <v>135.15</v>
       </c>
       <c r="L8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s">
         <v>105</v>
       </c>
       <c r="N8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9">
@@ -47362,52 +47578,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="I1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="J1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="L1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="M1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
+        <v>180</v>
+      </c>
+      <c r="B2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C2" t="n">
+        <v>141</v>
+      </c>
+      <c r="D2" t="n">
+        <v>168</v>
+      </c>
       <c r="E2" t="n">
         <v>9</v>
       </c>
@@ -47438,11 +47660,17 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
+        <v>160</v>
+      </c>
+      <c r="B3" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3" t="n">
+        <v>287</v>
+      </c>
+      <c r="D3" t="n">
+        <v>351</v>
+      </c>
       <c r="E3" t="n">
         <v>13</v>
       </c>
@@ -47473,11 +47701,17 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
+        <v>213</v>
+      </c>
+      <c r="B4" t="n">
+        <v>41</v>
+      </c>
+      <c r="C4" t="n">
+        <v>231</v>
+      </c>
+      <c r="D4" t="n">
+        <v>272</v>
+      </c>
       <c r="E4" t="n">
         <v>16</v>
       </c>
@@ -47508,11 +47742,17 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
+        <v>271</v>
+      </c>
+      <c r="B5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C5" t="n">
+        <v>203</v>
+      </c>
+      <c r="D5" t="n">
+        <v>222</v>
+      </c>
       <c r="E5" t="n">
         <v>6</v>
       </c>
@@ -47543,7 +47783,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B6" t="n">
         <v>151</v>
@@ -47554,24 +47794,12 @@
       <c r="D6" t="n">
         <v>1013</v>
       </c>
-      <c r="E6" t="n">
-        <v>44</v>
-      </c>
-      <c r="F6" t="n">
-        <v>48</v>
-      </c>
-      <c r="G6" t="n">
-        <v>92</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
       <c r="K6" t="n">
         <v>0</v>
       </c>
@@ -47599,7 +47827,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B8" t="n">
         <v>5</v>
@@ -47640,7 +47868,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B9" t="n">
         <v>23</v>
@@ -47681,7 +47909,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B10" t="n">
         <v>103</v>
@@ -47733,46 +47961,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="H1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="J1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="K1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="L1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="M1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="N1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
@@ -48036,7 +48264,7 @@
         <v>56</v>
       </c>
       <c r="N7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">

--- a/3_output/2026/w29/y2026_w29_weekly_report_output.xlsx
+++ b/3_output/2026/w29/y2026_w29_weekly_report_output.xlsx
@@ -3238,7 +3238,7 @@
         <v>56</v>
       </c>
       <c r="D23" s="26" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E23" s="26" t="s">
         <v>56</v>
@@ -3262,7 +3262,7 @@
         <v>56</v>
       </c>
       <c r="L23" s="26" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="M23" s="26" t="s">
         <v>56</v>
@@ -3376,13 +3376,13 @@
         <v>56</v>
       </c>
       <c r="H25" s="26" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="I25" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J25" s="26" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>56</v>
@@ -3553,7 +3553,7 @@
         <v>58</v>
       </c>
       <c r="D28" s="26" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>58</v>
@@ -3577,7 +3577,7 @@
         <v>58</v>
       </c>
       <c r="L28" s="26" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="M28" s="16" t="s">
         <v>58</v>
@@ -3679,7 +3679,7 @@
         <v>58</v>
       </c>
       <c r="D30" s="26" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="E30" s="16" t="s">
         <v>58</v>
@@ -3691,7 +3691,7 @@
         <v>58</v>
       </c>
       <c r="H30" s="26" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I30" s="16" t="s">
         <v>58</v>
@@ -3742,13 +3742,13 @@
         <v>58</v>
       </c>
       <c r="D31" s="26" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>58</v>
       </c>
       <c r="F31" s="26" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>58</v>
@@ -3805,7 +3805,7 @@
         <v>58</v>
       </c>
       <c r="D32" s="26" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>58</v>
@@ -3823,13 +3823,13 @@
         <v>58</v>
       </c>
       <c r="J32" s="26" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>58</v>
       </c>
       <c r="L32" s="26" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="M32" s="16" t="s">
         <v>58</v>
@@ -3886,7 +3886,7 @@
         <v>58</v>
       </c>
       <c r="J33" s="26" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>58</v>
@@ -3931,7 +3931,7 @@
         <v>58</v>
       </c>
       <c r="D34" s="26" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>58</v>
@@ -6887,7 +6887,7 @@
         <v>56</v>
       </c>
       <c r="D90" s="14" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="E90" s="14" t="s">
         <v>56</v>
@@ -6911,7 +6911,7 @@
         <v>56</v>
       </c>
       <c r="L90" s="14" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="M90" s="14" t="s">
         <v>56</v>
@@ -7025,19 +7025,19 @@
         <v>56</v>
       </c>
       <c r="H92" s="14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I92" s="14" t="s">
         <v>56</v>
       </c>
       <c r="J92" s="14" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="K92" s="14" t="s">
         <v>56</v>
       </c>
       <c r="L92" s="14" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M92" s="16" t="s">
         <v>56</v>
@@ -7100,7 +7100,7 @@
         <v>56</v>
       </c>
       <c r="L93" s="14" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="M93" s="16" t="s">
         <v>56</v>
@@ -7202,7 +7202,7 @@
         <v>58</v>
       </c>
       <c r="D95" s="14" t="n">
-        <v>5.66</v>
+        <v>6.34</v>
       </c>
       <c r="E95" s="14" t="s">
         <v>58</v>
@@ -7226,7 +7226,7 @@
         <v>58</v>
       </c>
       <c r="L95" s="14" t="n">
-        <v>5.52</v>
+        <v>5.6</v>
       </c>
       <c r="M95" s="16" t="s">
         <v>58</v>
@@ -7265,31 +7265,31 @@
         <v>58</v>
       </c>
       <c r="D96" s="14" t="n">
-        <v>10.48</v>
+        <v>10.46</v>
       </c>
       <c r="E96" s="14" t="s">
         <v>58</v>
       </c>
       <c r="F96" s="14" t="n">
-        <v>5.66</v>
+        <v>5.64</v>
       </c>
       <c r="G96" s="14" t="s">
         <v>58</v>
       </c>
       <c r="H96" s="14" t="n">
-        <v>8.52</v>
+        <v>8.5</v>
       </c>
       <c r="I96" s="14" t="s">
         <v>58</v>
       </c>
       <c r="J96" s="14" t="n">
-        <v>10.38</v>
+        <v>10.34</v>
       </c>
       <c r="K96" s="14" t="s">
         <v>58</v>
       </c>
       <c r="L96" s="14" t="n">
-        <v>7.86</v>
+        <v>7.84</v>
       </c>
       <c r="M96" s="16" t="s">
         <v>58</v>
@@ -7328,31 +7328,31 @@
         <v>58</v>
       </c>
       <c r="D97" s="14" t="n">
-        <v>10.98</v>
+        <v>10.84</v>
       </c>
       <c r="E97" s="14" t="s">
         <v>58</v>
       </c>
       <c r="F97" s="14" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="G97" s="14" t="s">
         <v>58</v>
       </c>
       <c r="H97" s="14" t="n">
-        <v>8.74</v>
+        <v>8.68</v>
       </c>
       <c r="I97" s="14" t="s">
         <v>58</v>
       </c>
       <c r="J97" s="14" t="n">
-        <v>12.16</v>
+        <v>12.12</v>
       </c>
       <c r="K97" s="14" t="s">
         <v>58</v>
       </c>
       <c r="L97" s="14" t="n">
-        <v>10.82</v>
+        <v>10.76</v>
       </c>
       <c r="M97" s="16" t="s">
         <v>58</v>
@@ -7391,31 +7391,31 @@
         <v>58</v>
       </c>
       <c r="D98" s="14" t="n">
-        <v>12.16</v>
+        <v>12.74</v>
       </c>
       <c r="E98" s="14" t="s">
         <v>58</v>
       </c>
       <c r="F98" s="14" t="n">
-        <v>12.56</v>
+        <v>13.3</v>
       </c>
       <c r="G98" s="14" t="s">
         <v>58</v>
       </c>
       <c r="H98" s="14" t="n">
-        <v>9.18</v>
+        <v>9.16</v>
       </c>
       <c r="I98" s="14" t="s">
         <v>58</v>
       </c>
       <c r="J98" s="14" t="n">
-        <v>17.74</v>
+        <v>17.48</v>
       </c>
       <c r="K98" s="14" t="s">
         <v>58</v>
       </c>
       <c r="L98" s="14" t="n">
-        <v>11.74</v>
+        <v>11.94</v>
       </c>
       <c r="M98" s="16" t="s">
         <v>58</v>
@@ -7454,31 +7454,31 @@
         <v>58</v>
       </c>
       <c r="D99" s="14" t="n">
-        <v>4.14</v>
+        <v>5.02</v>
       </c>
       <c r="E99" s="14" t="s">
         <v>58</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>8.62</v>
+        <v>8.58</v>
       </c>
       <c r="G99" s="14" t="s">
         <v>58</v>
       </c>
       <c r="H99" s="14" t="n">
-        <v>12.44</v>
+        <v>12.08</v>
       </c>
       <c r="I99" s="14" t="s">
         <v>58</v>
       </c>
       <c r="J99" s="14" t="n">
-        <v>13.16</v>
+        <v>15</v>
       </c>
       <c r="K99" s="14" t="s">
         <v>58</v>
       </c>
       <c r="L99" s="14" t="n">
-        <v>8.3</v>
+        <v>8.7</v>
       </c>
       <c r="M99" s="16" t="s">
         <v>58</v>
@@ -7517,7 +7517,7 @@
         <v>58</v>
       </c>
       <c r="D100" s="14" t="n">
-        <v>17.74</v>
+        <v>17.08</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>58</v>
@@ -7529,19 +7529,19 @@
         <v>58</v>
       </c>
       <c r="H100" s="14" t="n">
-        <v>10.06</v>
+        <v>9.92</v>
       </c>
       <c r="I100" s="14" t="s">
         <v>58</v>
       </c>
       <c r="J100" s="14" t="n">
-        <v>4.96</v>
+        <v>8.16</v>
       </c>
       <c r="K100" s="14" t="s">
         <v>58</v>
       </c>
       <c r="L100" s="14" t="n">
-        <v>7.12</v>
+        <v>7.42</v>
       </c>
       <c r="M100" s="16" t="s">
         <v>58</v>
@@ -7580,31 +7580,31 @@
         <v>58</v>
       </c>
       <c r="D101" s="14" t="n">
-        <v>7.24</v>
+        <v>6.7</v>
       </c>
       <c r="E101" s="14" t="s">
         <v>58</v>
       </c>
       <c r="F101" s="14" t="n">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="G101" s="14" t="s">
         <v>58</v>
       </c>
       <c r="H101" s="14" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="I101" s="14" t="s">
         <v>58</v>
       </c>
       <c r="J101" s="14" t="n">
-        <v>5.94</v>
+        <v>5.22</v>
       </c>
       <c r="K101" s="14" t="s">
         <v>58</v>
       </c>
       <c r="L101" s="14" t="n">
-        <v>5.04</v>
+        <v>4.84</v>
       </c>
       <c r="M101" s="16" t="s">
         <v>58</v>
@@ -46075,7 +46075,7 @@
         <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -46099,7 +46099,7 @@
         <v>56</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L5" t="s">
         <v>56</v>
@@ -46175,13 +46175,13 @@
         <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="H7" t="s">
         <v>56</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="J7" t="s">
         <v>56</v>
@@ -46295,7 +46295,7 @@
         <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
@@ -46319,7 +46319,7 @@
         <v>58</v>
       </c>
       <c r="K10" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="L10" t="s">
         <v>58</v>
@@ -46383,7 +46383,7 @@
         <v>58</v>
       </c>
       <c r="C12" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="D12" t="s">
         <v>58</v>
@@ -46395,7 +46395,7 @@
         <v>58</v>
       </c>
       <c r="G12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="H12" t="s">
         <v>58</v>
@@ -46427,13 +46427,13 @@
         <v>58</v>
       </c>
       <c r="C13" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="D13" t="s">
         <v>58</v>
       </c>
       <c r="E13" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="s">
         <v>58</v>
@@ -46471,7 +46471,7 @@
         <v>58</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D14" t="s">
         <v>58</v>
@@ -46489,13 +46489,13 @@
         <v>58</v>
       </c>
       <c r="I14" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="J14" t="s">
         <v>58</v>
       </c>
       <c r="K14" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="L14" t="s">
         <v>58</v>
@@ -46533,7 +46533,7 @@
         <v>58</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J15" t="s">
         <v>58</v>
@@ -46559,7 +46559,7 @@
         <v>58</v>
       </c>
       <c r="C16" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D16" t="s">
         <v>58</v>
@@ -48143,7 +48143,7 @@
         <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -48167,7 +48167,7 @@
         <v>56</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="L5" t="s">
         <v>56</v>
@@ -48243,19 +48243,19 @@
         <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H7" t="s">
         <v>56</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="s">
         <v>56</v>
       </c>
       <c r="K7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="L7" t="s">
         <v>56</v>
@@ -48299,7 +48299,7 @@
         <v>56</v>
       </c>
       <c r="K8" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="s">
         <v>56</v>
@@ -48363,7 +48363,7 @@
         <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>5.66</v>
+        <v>6.34</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
@@ -48387,7 +48387,7 @@
         <v>58</v>
       </c>
       <c r="K10" t="n">
-        <v>5.52</v>
+        <v>5.6</v>
       </c>
       <c r="L10" t="s">
         <v>58</v>
@@ -48407,31 +48407,31 @@
         <v>58</v>
       </c>
       <c r="C11" t="n">
-        <v>10.48</v>
+        <v>10.46</v>
       </c>
       <c r="D11" t="s">
         <v>58</v>
       </c>
       <c r="E11" t="n">
-        <v>5.66</v>
+        <v>5.64</v>
       </c>
       <c r="F11" t="s">
         <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>8.52</v>
+        <v>8.5</v>
       </c>
       <c r="H11" t="s">
         <v>58</v>
       </c>
       <c r="I11" t="n">
-        <v>10.38</v>
+        <v>10.34</v>
       </c>
       <c r="J11" t="s">
         <v>58</v>
       </c>
       <c r="K11" t="n">
-        <v>7.86</v>
+        <v>7.84</v>
       </c>
       <c r="L11" t="s">
         <v>58</v>
@@ -48451,31 +48451,31 @@
         <v>58</v>
       </c>
       <c r="C12" t="n">
-        <v>10.98</v>
+        <v>10.84</v>
       </c>
       <c r="D12" t="s">
         <v>58</v>
       </c>
       <c r="E12" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="F12" t="s">
         <v>58</v>
       </c>
       <c r="G12" t="n">
-        <v>8.74</v>
+        <v>8.68</v>
       </c>
       <c r="H12" t="s">
         <v>58</v>
       </c>
       <c r="I12" t="n">
-        <v>12.16</v>
+        <v>12.12</v>
       </c>
       <c r="J12" t="s">
         <v>58</v>
       </c>
       <c r="K12" t="n">
-        <v>10.82</v>
+        <v>10.76</v>
       </c>
       <c r="L12" t="s">
         <v>58</v>
@@ -48495,31 +48495,31 @@
         <v>58</v>
       </c>
       <c r="C13" t="n">
-        <v>12.16</v>
+        <v>12.74</v>
       </c>
       <c r="D13" t="s">
         <v>58</v>
       </c>
       <c r="E13" t="n">
-        <v>12.56</v>
+        <v>13.3</v>
       </c>
       <c r="F13" t="s">
         <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>9.18</v>
+        <v>9.16</v>
       </c>
       <c r="H13" t="s">
         <v>58</v>
       </c>
       <c r="I13" t="n">
-        <v>17.74</v>
+        <v>17.48</v>
       </c>
       <c r="J13" t="s">
         <v>58</v>
       </c>
       <c r="K13" t="n">
-        <v>11.74</v>
+        <v>11.94</v>
       </c>
       <c r="L13" t="s">
         <v>58</v>
@@ -48539,31 +48539,31 @@
         <v>58</v>
       </c>
       <c r="C14" t="n">
-        <v>4.14</v>
+        <v>5.02</v>
       </c>
       <c r="D14" t="s">
         <v>58</v>
       </c>
       <c r="E14" t="n">
-        <v>8.62</v>
+        <v>8.58</v>
       </c>
       <c r="F14" t="s">
         <v>58</v>
       </c>
       <c r="G14" t="n">
-        <v>12.44</v>
+        <v>12.08</v>
       </c>
       <c r="H14" t="s">
         <v>58</v>
       </c>
       <c r="I14" t="n">
-        <v>13.16</v>
+        <v>15</v>
       </c>
       <c r="J14" t="s">
         <v>58</v>
       </c>
       <c r="K14" t="n">
-        <v>8.3</v>
+        <v>8.7</v>
       </c>
       <c r="L14" t="s">
         <v>58</v>
@@ -48583,7 +48583,7 @@
         <v>58</v>
       </c>
       <c r="C15" t="n">
-        <v>17.74</v>
+        <v>17.08</v>
       </c>
       <c r="D15" t="s">
         <v>58</v>
@@ -48595,19 +48595,19 @@
         <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>10.06</v>
+        <v>9.92</v>
       </c>
       <c r="H15" t="s">
         <v>58</v>
       </c>
       <c r="I15" t="n">
-        <v>4.96</v>
+        <v>8.16</v>
       </c>
       <c r="J15" t="s">
         <v>58</v>
       </c>
       <c r="K15" t="n">
-        <v>7.12</v>
+        <v>7.42</v>
       </c>
       <c r="L15" t="s">
         <v>58</v>
@@ -48627,31 +48627,31 @@
         <v>58</v>
       </c>
       <c r="C16" t="n">
-        <v>7.24</v>
+        <v>6.7</v>
       </c>
       <c r="D16" t="s">
         <v>58</v>
       </c>
       <c r="E16" t="n">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="F16" t="s">
         <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="H16" t="s">
         <v>58</v>
       </c>
       <c r="I16" t="n">
-        <v>5.94</v>
+        <v>5.22</v>
       </c>
       <c r="J16" t="s">
         <v>58</v>
       </c>
       <c r="K16" t="n">
-        <v>5.04</v>
+        <v>4.84</v>
       </c>
       <c r="L16" t="s">
         <v>58</v>
